--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.84044</v>
+        <v>16.99154</v>
       </c>
       <c r="D2" t="n">
-        <v>16.16407</v>
+        <v>15.85751</v>
       </c>
       <c r="E2" t="n">
-        <v>16.68111</v>
+        <v>16.45151</v>
       </c>
       <c r="F2" t="n">
-        <v>21.71728</v>
+        <v>21.89922</v>
       </c>
       <c r="G2" t="n">
-        <v>22.07149</v>
+        <v>22.49771</v>
       </c>
       <c r="H2" t="n">
-        <v>34.61057</v>
+        <v>34.53887</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.4952</v>
+        <v>16.73188</v>
       </c>
       <c r="D3" t="n">
-        <v>16.15291</v>
+        <v>15.92963</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6429</v>
+        <v>16.65093</v>
       </c>
       <c r="F3" t="n">
-        <v>21.96396</v>
+        <v>21.92585</v>
       </c>
       <c r="G3" t="n">
-        <v>21.80065</v>
+        <v>22.61055</v>
       </c>
       <c r="H3" t="n">
-        <v>34.40813</v>
+        <v>34.53029</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.78606</v>
+        <v>16.88885</v>
       </c>
       <c r="D4" t="n">
-        <v>16.06774</v>
+        <v>16.02547</v>
       </c>
       <c r="E4" t="n">
-        <v>16.79961</v>
+        <v>16.40196</v>
       </c>
       <c r="F4" t="n">
-        <v>21.86456</v>
+        <v>21.94505</v>
       </c>
       <c r="G4" t="n">
-        <v>22.14955</v>
+        <v>21.98163</v>
       </c>
       <c r="H4" t="n">
-        <v>34.3028</v>
+        <v>35.17453</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.97223</v>
+        <v>17.00366</v>
       </c>
       <c r="D5" t="n">
-        <v>15.97354</v>
+        <v>16.03607</v>
       </c>
       <c r="E5" t="n">
-        <v>16.93917</v>
+        <v>16.75187</v>
       </c>
       <c r="F5" t="n">
-        <v>22.22312</v>
+        <v>21.81974</v>
       </c>
       <c r="G5" t="n">
-        <v>22.23061</v>
+        <v>22.01104</v>
       </c>
       <c r="H5" t="n">
-        <v>35.09395</v>
+        <v>34.64216</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.59469</v>
+        <v>16.86664</v>
       </c>
       <c r="D6" t="n">
-        <v>16.53118</v>
+        <v>16.01313</v>
       </c>
       <c r="E6" t="n">
-        <v>16.75309</v>
+        <v>16.43049</v>
       </c>
       <c r="F6" t="n">
-        <v>21.55576</v>
+        <v>21.58697</v>
       </c>
       <c r="G6" t="n">
-        <v>21.86457</v>
+        <v>22.23347</v>
       </c>
       <c r="H6" t="n">
-        <v>35.27506</v>
+        <v>35.59185</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.02121</v>
+        <v>17.12651</v>
       </c>
       <c r="D7" t="n">
-        <v>15.70984</v>
+        <v>16.35237</v>
       </c>
       <c r="E7" t="n">
-        <v>16.80071</v>
+        <v>16.37104</v>
       </c>
       <c r="F7" t="n">
-        <v>22.29397</v>
+        <v>21.97573</v>
       </c>
       <c r="G7" t="n">
-        <v>22.2144</v>
+        <v>21.95212</v>
       </c>
       <c r="H7" t="n">
-        <v>34.94352</v>
+        <v>34.23709</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.97766</v>
+        <v>16.59052</v>
       </c>
       <c r="D8" t="n">
-        <v>16.25796</v>
+        <v>16.19536</v>
       </c>
       <c r="E8" t="n">
-        <v>16.7054</v>
+        <v>16.42146</v>
       </c>
       <c r="F8" t="n">
-        <v>22.13043</v>
+        <v>22.36569</v>
       </c>
       <c r="G8" t="n">
-        <v>22.66996</v>
+        <v>22.39537</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47197</v>
+        <v>35.2827</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.80407</v>
+        <v>17.00346</v>
       </c>
       <c r="D9" t="n">
-        <v>16.06987</v>
+        <v>16.16014</v>
       </c>
       <c r="E9" t="n">
-        <v>16.55442</v>
+        <v>16.41429</v>
       </c>
       <c r="F9" t="n">
-        <v>21.9777</v>
+        <v>21.4454</v>
       </c>
       <c r="G9" t="n">
-        <v>21.54787</v>
+        <v>22.1424</v>
       </c>
       <c r="H9" t="n">
-        <v>34.59044</v>
+        <v>34.52062</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.90244</v>
+        <v>17.18577</v>
       </c>
       <c r="D10" t="n">
-        <v>16.14877</v>
+        <v>16.21655</v>
       </c>
       <c r="E10" t="n">
-        <v>16.43772</v>
+        <v>16.49445</v>
       </c>
       <c r="F10" t="n">
-        <v>21.62072</v>
+        <v>21.92959</v>
       </c>
       <c r="G10" t="n">
-        <v>22.08371</v>
+        <v>21.894</v>
       </c>
       <c r="H10" t="n">
-        <v>34.35454</v>
+        <v>35.09757</v>
       </c>
     </row>
   </sheetData>
